--- a/output/第10期計画_3町別の論点整理.xlsx
+++ b/output/第10期計画_3町別の論点整理.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>暫定の算定では月額6,684円で第9期の6,400円を284円上回る。基金の取崩しにより下げる余地がある。</t>
+          <t>暫定の算定では月額6,755円で第9期の6,400円を355円上回る。基金の取崩しにより下げる余地がある。</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>暫定の算定では月額6,684円で第9期の6,400円を284円上回る。令和6年度末の基金残高231,689,018円は条例の上限を26,492,172円上回っている。</t>
+          <t>暫定の算定では月額6,755円で第9期の6,400円を355円上回る。令和6年度末の基金残高231,689,018円は条例の上限を26,492,172円上回っている。</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">

--- a/output/第10期計画_3町別の論点整理.xlsx
+++ b/output/第10期計画_3町別の論点整理.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>暫定の算定では月額6,755円で第9期の6,400円を355円上回る。基金の取崩しにより下げる余地がある。</t>
+          <t>暫定の算定では月額6,740円で第9期の6,400円を340円上回る。基金の取崩しにより下げる余地がある。</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>暫定の算定では月額6,755円で第9期の6,400円を355円上回る。令和6年度末の基金残高231,689,018円は条例の上限を26,492,172円上回っている。</t>
+          <t>暫定の算定では月額6,740円で第9期の6,400円を340円上回る。令和6年度末の基金残高231,689,018円は条例の上限を26,492,172円上回っている。</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">

--- a/output/第10期計画_3町別の論点整理.xlsx
+++ b/output/第10期計画_3町別の論点整理.xlsx
@@ -3336,7 +3336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3753,11 +3753,222 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会の第10期中のサービス提供方針</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>ひだまりの里（老健）・羽衣園（特養）を運営する旭川福祉事業会の第10期中の介護サービス提供方針。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>1法人が東川町の施設サービスの相当部分を担っており、方針の変更は施設サービス見込量に直接効く。介護人材実態調査には職員個票55人分を提出しており区域内で最も多い。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ひだまりの里デイサービス（地域密着型）の再開見込み</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>休止中のひだまりの里デイサービス（地域密着型）を第10期中に再開する見込みがあるか。</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>北海道の指定事業所一覧（令和8年7月1日現在）の地域密着型通所介護は4事業所であり、当該事業所は掲載されていない。計画素案が地域密着型通所介護の給付費▲27.0％の理由を「稼働率の低下が疑われる」としている記述を、休止という事実に置き換えられる可能性がある。</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ひだまりの里（老健）・羽衣園（特養）の定員の変更予定</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>令和9〜11年度の定員等の変更予定。</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>施設サービスは1人あたり給付費が高く、定員の増減がそのまま給付費と保険料に効く。介護老人保健施設の定員は東川町64人・美瑛町67人・東神楽町23人である。</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護の公募</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>第10期中に公募する考えがあるか。</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>平成24年度の創設から令和6年度まで13年間、区域内に事業所がない。上川中部圏域では令和8年に68.0人／月の見込みである。整備する場合、見込量に新たなサービスが加わり保険料が上がる（決定3）。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>アゼリアハイツの空室問題への対応</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型特養の空室問題への今後の対応。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>空室が続く場合、地域密着型介護老人福祉施設の見込量を定員どおりに置くと過大となる。</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>空室のショートステイ利用・広域型への転換</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>空室のショートステイ利用、地域密着型から広域型への転換等の検討状況。</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>転換した場合、地域密着型の定員が減り介護老人福祉施設の定員が増える。1人あたり給付費が異なるため保険料に効く。指定権者が広域連合から北海道に移るため、第7章（地域密着型サービスの指定）の記述にも影響する。</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>グループホームびえいの郷の定員減への対応</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>定員減（18人から9人）を踏まえ、第10期中に減少分を補う考えがあるか。あわせて減員の時期と、現在の定員データへの反映の有無。</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の定員は、見える化D26で令和4年度以降99人、計画作成支援ツールで3町計86人（美瑛町21人）である。定員減が既に反映されているかの確認を要する（確認事項No.78）。定員は見込量の上限となる。</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>注1）「受託者の見立て」は現時点の資料による推測を含みます。各町のご説明により置き換えます。
-注2）町別の給付実績のうち令和7年度は3町の合計が広域連合の合計と一致しないため（確認事項No.46）、給付額を用いた論点は掲げていません。</t>
+注2）町別の給付実績のうち令和7年度は3町の合計が広域連合の合計と一致しないため（確認事項No.46）、給付額を用いた論点は掲げていません。
+注3）No.13以降は、令和8年9月3日の広域連合の内部確認結果によりご指示のあった施設整備・サービス提供方針の確認事項です。回答はサービス見込量及び保険料算定に直接反映します。</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3976,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3777,7 +3988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4088,8 +4299,40 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>第10期中の地域密着型サービス等の変更予定</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>第10期中に予定又は検討している地域密着型サービス等の新設・廃止・定員変更等の有無。地域密着型サービスの指定権者は広域連合であり、現在の見込量は既存の定員が第10期中も維持されることを前提としている。</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>①変更の予定なし
+②変更の予定あり（年度・内容を特定する）
+③検討中（決定の時期を示す）</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>令和8年11月</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>決定3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>注）「決定1」「決定2」は業務工程管理表の確認事項の番号、「No.」は同表 03_確認事項一覧の番号です。</t>
         </is>
@@ -4098,8 +4341,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
